--- a/docs/final_data_dictionary.xlsx
+++ b/docs/final_data_dictionary.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Pending: instructor extract and field mapping not provided</t>
+          <t>Not applicable: no instructor extract supplied; mapped directly from ARMD Dryad version 403223</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
